--- a/output/Data and Chart Outputs/au_rooftop_solar.xlsx
+++ b/output/Data and Chart Outputs/au_rooftop_solar.xlsx
@@ -158,7 +158,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Australia rooftop solar installed per month by state (Clean Energy Regulator) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Australia rooftop solar installed per month by state (Clean Energy Regulator) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -188,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$69</f>
+              <f>'Chart'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -216,12 +217,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$69</f>
+              <f>'Chart'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -244,12 +245,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$69</f>
+              <f>'Chart'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -272,12 +273,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$69</f>
+              <f>'Chart'!$E$2:$E$70</f>
             </numRef>
           </val>
         </ser>
@@ -300,12 +301,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$69</f>
+              <f>'Chart'!$F$2:$F$70</f>
             </numRef>
           </val>
         </ser>
@@ -328,12 +329,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$69</f>
+              <f>'Chart'!$G$2:$G$70</f>
             </numRef>
           </val>
         </ser>
@@ -356,12 +357,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$69</f>
+              <f>'Chart'!$H$2:$H$70</f>
             </numRef>
           </val>
         </ser>
@@ -384,12 +385,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$69</f>
+              <f>'Chart'!$I$2:$I$70</f>
             </numRef>
           </val>
         </ser>
@@ -489,7 +490,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Australia home batteries installed per month by state (Clean Energy Regulator) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Australia home batteries installed per month by state (Clean Energy Regulator) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -519,12 +521,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Home batteries'!$A$2:$A$15</f>
+              <f>'Chart - Home batteries'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Home batteries'!$B$2:$B$15</f>
+              <f>'Chart - Home batteries'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -547,12 +549,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Home batteries'!$A$2:$A$15</f>
+              <f>'Chart - Home batteries'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Home batteries'!$C$2:$C$15</f>
+              <f>'Chart - Home batteries'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -575,12 +577,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Home batteries'!$A$2:$A$15</f>
+              <f>'Chart - Home batteries'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Home batteries'!$D$2:$D$15</f>
+              <f>'Chart - Home batteries'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -603,12 +605,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Home batteries'!$A$2:$A$15</f>
+              <f>'Chart - Home batteries'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Home batteries'!$E$2:$E$15</f>
+              <f>'Chart - Home batteries'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -631,12 +633,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Home batteries'!$A$2:$A$15</f>
+              <f>'Chart - Home batteries'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Home batteries'!$F$2:$F$15</f>
+              <f>'Chart - Home batteries'!$F$2:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -659,12 +661,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Home batteries'!$A$2:$A$15</f>
+              <f>'Chart - Home batteries'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Home batteries'!$G$2:$G$15</f>
+              <f>'Chart - Home batteries'!$G$2:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -687,12 +689,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Home batteries'!$A$2:$A$15</f>
+              <f>'Chart - Home batteries'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Home batteries'!$H$2:$H$15</f>
+              <f>'Chart - Home batteries'!$H$2:$H$16</f>
             </numRef>
           </val>
         </ser>
@@ -715,12 +717,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Home batteries'!$A$2:$A$15</f>
+              <f>'Chart - Home batteries'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Home batteries'!$I$2:$I$15</f>
+              <f>'Chart - Home batteries'!$I$2:$I$16</f>
             </numRef>
           </val>
         </ser>
@@ -1196,7 +1198,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Australia by state, monthly, Jan 2011 to Aug 2026. Battery installs only from Jul 2025 in this file.</t>
+          <t>Australia by state, monthly, Jan 2011 to Sep 2026. Battery installs only from Jul 2025 in this file.</t>
         </is>
       </c>
     </row>
@@ -1225,21 +1227,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Solar installs file Last-Modified: Wed, 16 Sep 2026 23:10:37 GMT</t>
+          <t>Solar installs file Last-Modified: Mon, 19 Oct 2026 23:39:40 GMT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solar capacity file Last-Modified: Wed, 16 Sep 2026 23:05:32 GMT</t>
+          <t>Solar capacity file Last-Modified: Mon, 19 Oct 2026 23:47:39 GMT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Battery installs file Last-Modified: Wed, 16 Sep 2026 23:11:33 GMT</t>
+          <t>Battery installs file Last-Modified: Mon, 19 Oct 2026 23:41:42 GMT</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2675,7 +2677,7 @@
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>106.24</v>
+        <v>106.26</v>
       </c>
       <c r="C49" t="n">
         <v>69.52</v>
@@ -2707,7 +2709,7 @@
         <v>46.55</v>
       </c>
       <c r="C50" t="n">
-        <v>37.24</v>
+        <v>37.25</v>
       </c>
       <c r="D50" t="n">
         <v>53.08</v>
@@ -2762,10 +2764,10 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>74.09</v>
+        <v>74.28</v>
       </c>
       <c r="C52" t="n">
-        <v>52.9</v>
+        <v>52.93</v>
       </c>
       <c r="D52" t="n">
         <v>57.01</v>
@@ -2791,7 +2793,7 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>57.37</v>
+        <v>57.38</v>
       </c>
       <c r="C53" t="n">
         <v>42.54</v>
@@ -2806,7 +2808,7 @@
         <v>19.4</v>
       </c>
       <c r="G53" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="H53" t="n">
         <v>3.31</v>
@@ -2820,16 +2822,16 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>57.5</v>
+        <v>57.54</v>
       </c>
       <c r="C54" t="n">
-        <v>44.39</v>
+        <v>44.46</v>
       </c>
       <c r="D54" t="n">
-        <v>61.52</v>
+        <v>61.71</v>
       </c>
       <c r="E54" t="n">
-        <v>18.99</v>
+        <v>19.02</v>
       </c>
       <c r="F54" t="n">
         <v>21.48</v>
@@ -2849,7 +2851,7 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>49.72</v>
+        <v>49.78</v>
       </c>
       <c r="C55" t="n">
         <v>34.09</v>
@@ -2878,13 +2880,13 @@
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>62.63</v>
+        <v>62.65</v>
       </c>
       <c r="C56" t="n">
-        <v>45.54</v>
+        <v>45.56</v>
       </c>
       <c r="D56" t="n">
-        <v>61.29</v>
+        <v>61.3</v>
       </c>
       <c r="E56" t="n">
         <v>24.31</v>
@@ -2907,19 +2909,19 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>57.18</v>
+        <v>57.21</v>
       </c>
       <c r="C57" t="n">
-        <v>43.56</v>
+        <v>43.68</v>
       </c>
       <c r="D57" t="n">
-        <v>53.62</v>
+        <v>53.72</v>
       </c>
       <c r="E57" t="n">
-        <v>19.44</v>
+        <v>19.46</v>
       </c>
       <c r="F57" t="n">
-        <v>18.05</v>
+        <v>18.17</v>
       </c>
       <c r="G57" t="n">
         <v>4.01</v>
@@ -2936,19 +2938,19 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>70.06</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>49.08</v>
+        <v>49.47</v>
       </c>
       <c r="D58" t="n">
-        <v>61.73</v>
+        <v>62</v>
       </c>
       <c r="E58" t="n">
-        <v>23.7</v>
+        <v>24.1</v>
       </c>
       <c r="F58" t="n">
-        <v>21.29</v>
+        <v>21.44</v>
       </c>
       <c r="G58" t="n">
         <v>5.04</v>
@@ -2965,25 +2967,25 @@
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>75.48999999999999</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="C59" t="n">
-        <v>58.06</v>
+        <v>58.23</v>
       </c>
       <c r="D59" t="n">
-        <v>66.44</v>
+        <v>66.59</v>
       </c>
       <c r="E59" t="n">
-        <v>25.08</v>
+        <v>25.19</v>
       </c>
       <c r="F59" t="n">
-        <v>25.58</v>
+        <v>25.6</v>
       </c>
       <c r="G59" t="n">
         <v>4.53</v>
       </c>
       <c r="H59" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I59" t="n">
         <v>1.39</v>
@@ -2994,25 +2996,25 @@
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>85.23999999999999</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="C60" t="n">
-        <v>55.94</v>
+        <v>56.23</v>
       </c>
       <c r="D60" t="n">
-        <v>71.42</v>
+        <v>71.59</v>
       </c>
       <c r="E60" t="n">
-        <v>26.62</v>
+        <v>26.67</v>
       </c>
       <c r="F60" t="n">
-        <v>28.08</v>
+        <v>28.32</v>
       </c>
       <c r="G60" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="H60" t="n">
-        <v>5.3</v>
+        <v>5.31</v>
       </c>
       <c r="I60" t="n">
         <v>1.67</v>
@@ -3023,28 +3025,28 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>108.5</v>
+        <v>108.91</v>
       </c>
       <c r="C61" t="n">
-        <v>72</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>83.45</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>35.39</v>
+        <v>35.68</v>
       </c>
       <c r="F61" t="n">
-        <v>31.49</v>
+        <v>31.66</v>
       </c>
       <c r="G61" t="n">
         <v>5.88</v>
       </c>
       <c r="H61" t="n">
-        <v>7.58</v>
+        <v>7.6</v>
       </c>
       <c r="I61" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="62">
@@ -3052,22 +3054,22 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>53.82</v>
+        <v>53.92</v>
       </c>
       <c r="C62" t="n">
-        <v>33.98</v>
+        <v>34.26</v>
       </c>
       <c r="D62" t="n">
-        <v>49.27</v>
+        <v>49.48</v>
       </c>
       <c r="E62" t="n">
-        <v>16.53</v>
+        <v>16.56</v>
       </c>
       <c r="F62" t="n">
-        <v>21.65</v>
+        <v>21.7</v>
       </c>
       <c r="G62" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="H62" t="n">
         <v>3.3</v>
@@ -3081,28 +3083,28 @@
         <v>46054</v>
       </c>
       <c r="B63" t="n">
-        <v>79.97</v>
+        <v>80.28</v>
       </c>
       <c r="C63" t="n">
-        <v>53.61</v>
+        <v>54.38</v>
       </c>
       <c r="D63" t="n">
-        <v>69.16</v>
+        <v>69.53</v>
       </c>
       <c r="E63" t="n">
-        <v>26.89</v>
+        <v>27.02</v>
       </c>
       <c r="F63" t="n">
-        <v>28.07</v>
+        <v>28.44</v>
       </c>
       <c r="G63" t="n">
         <v>4.6</v>
       </c>
       <c r="H63" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="I63" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="64">
@@ -3110,28 +3112,28 @@
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>108.43</v>
+        <v>108.96</v>
       </c>
       <c r="C64" t="n">
-        <v>63.25</v>
+        <v>64.08</v>
       </c>
       <c r="D64" t="n">
-        <v>94.22</v>
+        <v>94.83</v>
       </c>
       <c r="E64" t="n">
-        <v>35.24</v>
+        <v>35.38</v>
       </c>
       <c r="F64" t="n">
-        <v>33.35</v>
+        <v>33.56</v>
       </c>
       <c r="G64" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="H64" t="n">
-        <v>6</v>
+        <v>6.02</v>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="65">
@@ -3139,28 +3141,28 @@
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>153.08</v>
+        <v>155.2</v>
       </c>
       <c r="C65" t="n">
-        <v>93.44</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>124.15</v>
+        <v>125.2</v>
       </c>
       <c r="E65" t="n">
-        <v>47.75</v>
+        <v>48.31</v>
       </c>
       <c r="F65" t="n">
-        <v>44.21</v>
+        <v>44.75</v>
       </c>
       <c r="G65" t="n">
-        <v>7.09</v>
+        <v>7.11</v>
       </c>
       <c r="H65" t="n">
-        <v>10.03</v>
+        <v>10.17</v>
       </c>
       <c r="I65" t="n">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="66">
@@ -3168,28 +3170,28 @@
         <v>46143</v>
       </c>
       <c r="B66" t="n">
-        <v>63.92</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C66" t="n">
-        <v>41.45</v>
+        <v>43.04</v>
       </c>
       <c r="D66" t="n">
-        <v>66.84</v>
+        <v>67.62</v>
       </c>
       <c r="E66" t="n">
-        <v>24.26</v>
+        <v>24.76</v>
       </c>
       <c r="F66" t="n">
-        <v>32.26</v>
+        <v>32.7</v>
       </c>
       <c r="G66" t="n">
-        <v>4.56</v>
+        <v>4.68</v>
       </c>
       <c r="H66" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="67">
@@ -3197,28 +3199,28 @@
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>83.44</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="C67" t="n">
-        <v>41.77</v>
+        <v>44.95</v>
       </c>
       <c r="D67" t="n">
-        <v>87.73999999999999</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>23.38</v>
+        <v>24.06</v>
       </c>
       <c r="F67" t="n">
-        <v>32.82</v>
+        <v>33.94</v>
       </c>
       <c r="G67" t="n">
-        <v>4.25</v>
+        <v>4.32</v>
       </c>
       <c r="H67" t="n">
-        <v>4.53</v>
+        <v>4.61</v>
       </c>
       <c r="I67" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="68">
@@ -3226,28 +3228,28 @@
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>74.56</v>
+        <v>80.56</v>
       </c>
       <c r="C68" t="n">
-        <v>40.15</v>
+        <v>46.92</v>
       </c>
       <c r="D68" t="n">
-        <v>82.29000000000001</v>
+        <v>85.58</v>
       </c>
       <c r="E68" t="n">
-        <v>22.28</v>
+        <v>24.22</v>
       </c>
       <c r="F68" t="n">
-        <v>35.72</v>
+        <v>38.11</v>
       </c>
       <c r="G68" t="n">
-        <v>4.14</v>
+        <v>4.47</v>
       </c>
       <c r="H68" t="n">
-        <v>5.38</v>
+        <v>5.74</v>
       </c>
       <c r="I68" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="69">
@@ -3255,28 +3257,57 @@
         <v>46235</v>
       </c>
       <c r="B69" t="n">
-        <v>42.85</v>
+        <v>67.37</v>
       </c>
       <c r="C69" t="n">
-        <v>12.36</v>
+        <v>33.62</v>
       </c>
       <c r="D69" t="n">
-        <v>48.93</v>
+        <v>68.02</v>
       </c>
       <c r="E69" t="n">
-        <v>13.89</v>
+        <v>21.91</v>
       </c>
       <c r="F69" t="n">
-        <v>22.96</v>
+        <v>33.63</v>
       </c>
       <c r="G69" t="n">
-        <v>3.21</v>
+        <v>4.57</v>
       </c>
       <c r="H69" t="n">
-        <v>2.78</v>
+        <v>4.44</v>
       </c>
       <c r="I69" t="n">
-        <v>0.51</v>
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="C70" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="D70" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="E70" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="F70" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -3291,7 +3322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3349,19 +3380,19 @@
         <v>45839</v>
       </c>
       <c r="B2" t="n">
-        <v>10210</v>
+        <v>10220</v>
       </c>
       <c r="C2" t="n">
-        <v>5977</v>
+        <v>5978</v>
       </c>
       <c r="D2" t="n">
-        <v>5639</v>
+        <v>5640</v>
       </c>
       <c r="E2" t="n">
-        <v>4448</v>
+        <v>4449</v>
       </c>
       <c r="F2" t="n">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="G2" t="n">
         <v>376</v>
@@ -3378,16 +3409,16 @@
         <v>45870</v>
       </c>
       <c r="B3" t="n">
-        <v>8456</v>
+        <v>8460</v>
       </c>
       <c r="C3" t="n">
-        <v>5266</v>
+        <v>5272</v>
       </c>
       <c r="D3" t="n">
-        <v>4531</v>
+        <v>4535</v>
       </c>
       <c r="E3" t="n">
-        <v>3285</v>
+        <v>3291</v>
       </c>
       <c r="F3" t="n">
         <v>3326</v>
@@ -3407,28 +3438,28 @@
         <v>45901</v>
       </c>
       <c r="B4" t="n">
-        <v>10570</v>
+        <v>10600</v>
       </c>
       <c r="C4" t="n">
-        <v>6195</v>
+        <v>6221</v>
       </c>
       <c r="D4" t="n">
-        <v>5559</v>
+        <v>5570</v>
       </c>
       <c r="E4" t="n">
-        <v>3983</v>
+        <v>4002</v>
       </c>
       <c r="F4" t="n">
-        <v>3704</v>
+        <v>3711</v>
       </c>
       <c r="G4" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H4" t="n">
         <v>580</v>
       </c>
       <c r="I4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5">
@@ -3436,22 +3467,22 @@
         <v>45931</v>
       </c>
       <c r="B5" t="n">
-        <v>12066</v>
+        <v>12092</v>
       </c>
       <c r="C5" t="n">
-        <v>7727</v>
+        <v>7770</v>
       </c>
       <c r="D5" t="n">
-        <v>6798</v>
+        <v>6814</v>
       </c>
       <c r="E5" t="n">
-        <v>4359</v>
+        <v>4375</v>
       </c>
       <c r="F5" t="n">
-        <v>4554</v>
+        <v>4558</v>
       </c>
       <c r="G5" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H5" t="n">
         <v>667</v>
@@ -3465,25 +3496,25 @@
         <v>45962</v>
       </c>
       <c r="B6" t="n">
-        <v>13201</v>
+        <v>13238</v>
       </c>
       <c r="C6" t="n">
-        <v>7921</v>
+        <v>7961</v>
       </c>
       <c r="D6" t="n">
-        <v>7344</v>
+        <v>7359</v>
       </c>
       <c r="E6" t="n">
-        <v>4447</v>
+        <v>4467</v>
       </c>
       <c r="F6" t="n">
-        <v>4529</v>
+        <v>4537</v>
       </c>
       <c r="G6" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H6" t="n">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="I6" t="n">
         <v>114</v>
@@ -3494,25 +3525,25 @@
         <v>45992</v>
       </c>
       <c r="B7" t="n">
-        <v>15600</v>
+        <v>15652</v>
       </c>
       <c r="C7" t="n">
-        <v>10237</v>
+        <v>10292</v>
       </c>
       <c r="D7" t="n">
-        <v>8565</v>
+        <v>8586</v>
       </c>
       <c r="E7" t="n">
-        <v>4844</v>
+        <v>4867</v>
       </c>
       <c r="F7" t="n">
-        <v>4482</v>
+        <v>4494</v>
       </c>
       <c r="G7" t="n">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H7" t="n">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="I7" t="n">
         <v>155</v>
@@ -3523,22 +3554,22 @@
         <v>46023</v>
       </c>
       <c r="B8" t="n">
-        <v>9919</v>
+        <v>9942</v>
       </c>
       <c r="C8" t="n">
-        <v>5195</v>
+        <v>5248</v>
       </c>
       <c r="D8" t="n">
-        <v>5898</v>
+        <v>5907</v>
       </c>
       <c r="E8" t="n">
-        <v>3046</v>
+        <v>3057</v>
       </c>
       <c r="F8" t="n">
-        <v>3686</v>
+        <v>3691</v>
       </c>
       <c r="G8" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H8" t="n">
         <v>476</v>
@@ -3552,25 +3583,25 @@
         <v>46054</v>
       </c>
       <c r="B9" t="n">
-        <v>14167</v>
+        <v>14209</v>
       </c>
       <c r="C9" t="n">
-        <v>8318</v>
+        <v>8388</v>
       </c>
       <c r="D9" t="n">
-        <v>8257</v>
+        <v>8267</v>
       </c>
       <c r="E9" t="n">
-        <v>4283</v>
+        <v>4294</v>
       </c>
       <c r="F9" t="n">
-        <v>4448</v>
+        <v>4458</v>
       </c>
       <c r="G9" t="n">
         <v>392</v>
       </c>
       <c r="H9" t="n">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="I9" t="n">
         <v>81</v>
@@ -3581,28 +3612,28 @@
         <v>46082</v>
       </c>
       <c r="B10" t="n">
-        <v>19894</v>
+        <v>19979</v>
       </c>
       <c r="C10" t="n">
-        <v>11530</v>
+        <v>11666</v>
       </c>
       <c r="D10" t="n">
-        <v>11343</v>
+        <v>11373</v>
       </c>
       <c r="E10" t="n">
-        <v>5468</v>
+        <v>5501</v>
       </c>
       <c r="F10" t="n">
-        <v>5233</v>
+        <v>5251</v>
       </c>
       <c r="G10" t="n">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="H10" t="n">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="I10" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
@@ -3610,28 +3641,28 @@
         <v>46113</v>
       </c>
       <c r="B11" t="n">
-        <v>30753</v>
+        <v>31072</v>
       </c>
       <c r="C11" t="n">
-        <v>19253</v>
+        <v>19844</v>
       </c>
       <c r="D11" t="n">
-        <v>18030</v>
+        <v>18227</v>
       </c>
       <c r="E11" t="n">
-        <v>8361</v>
+        <v>8454</v>
       </c>
       <c r="F11" t="n">
-        <v>6701</v>
+        <v>6771</v>
       </c>
       <c r="G11" t="n">
-        <v>895</v>
+        <v>911</v>
       </c>
       <c r="H11" t="n">
-        <v>1576</v>
+        <v>1599</v>
       </c>
       <c r="I11" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -3639,28 +3670,28 @@
         <v>46143</v>
       </c>
       <c r="B12" t="n">
-        <v>7061</v>
+        <v>7164</v>
       </c>
       <c r="C12" t="n">
-        <v>4274</v>
+        <v>4454</v>
       </c>
       <c r="D12" t="n">
-        <v>4674</v>
+        <v>4727</v>
       </c>
       <c r="E12" t="n">
-        <v>2609</v>
+        <v>2643</v>
       </c>
       <c r="F12" t="n">
-        <v>3899</v>
+        <v>3940</v>
       </c>
       <c r="G12" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H12" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="I12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -3668,28 +3699,28 @@
         <v>46174</v>
       </c>
       <c r="B13" t="n">
-        <v>9244</v>
+        <v>9718</v>
       </c>
       <c r="C13" t="n">
-        <v>4897</v>
+        <v>5412</v>
       </c>
       <c r="D13" t="n">
-        <v>6582</v>
+        <v>6728</v>
       </c>
       <c r="E13" t="n">
-        <v>2864</v>
+        <v>2997</v>
       </c>
       <c r="F13" t="n">
-        <v>3809</v>
+        <v>3941</v>
       </c>
       <c r="G13" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="H13" t="n">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="I13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -3697,28 +3728,28 @@
         <v>46204</v>
       </c>
       <c r="B14" t="n">
-        <v>9352</v>
+        <v>10204</v>
       </c>
       <c r="C14" t="n">
-        <v>4747</v>
+        <v>5832</v>
       </c>
       <c r="D14" t="n">
-        <v>6608</v>
+        <v>7035</v>
       </c>
       <c r="E14" t="n">
-        <v>2999</v>
+        <v>3290</v>
       </c>
       <c r="F14" t="n">
-        <v>4059</v>
+        <v>4316</v>
       </c>
       <c r="G14" t="n">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="H14" t="n">
-        <v>628</v>
+        <v>691</v>
       </c>
       <c r="I14" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -3726,28 +3757,57 @@
         <v>46235</v>
       </c>
       <c r="B15" t="n">
-        <v>5019</v>
+        <v>9160</v>
       </c>
       <c r="C15" t="n">
-        <v>1105</v>
+        <v>4417</v>
       </c>
       <c r="D15" t="n">
-        <v>3498</v>
+        <v>6058</v>
       </c>
       <c r="E15" t="n">
-        <v>1601</v>
+        <v>3140</v>
       </c>
       <c r="F15" t="n">
-        <v>2111</v>
+        <v>3775</v>
       </c>
       <c r="G15" t="n">
-        <v>168</v>
+        <v>301</v>
       </c>
       <c r="H15" t="n">
-        <v>285</v>
+        <v>586</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5444</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1274</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3752</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1631</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2281</v>
+      </c>
+      <c r="G16" t="n">
+        <v>124</v>
+      </c>
+      <c r="H16" t="n">
+        <v>330</v>
+      </c>
+      <c r="I16" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3762,7 +3822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J189"/>
+  <dimension ref="A1:J190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9146,7 +9206,7 @@
         <v>2382</v>
       </c>
       <c r="F168" t="n">
-        <v>3319</v>
+        <v>3320</v>
       </c>
       <c r="G168" t="n">
         <v>522</v>
@@ -9158,7 +9218,7 @@
         <v>73</v>
       </c>
       <c r="J168" t="n">
-        <v>26826</v>
+        <v>26827</v>
       </c>
     </row>
     <row r="169">
@@ -9166,7 +9226,7 @@
         <v>45627</v>
       </c>
       <c r="B169" t="n">
-        <v>8640</v>
+        <v>8641</v>
       </c>
       <c r="C169" t="n">
         <v>6520</v>
@@ -9190,7 +9250,7 @@
         <v>111</v>
       </c>
       <c r="J169" t="n">
-        <v>28131</v>
+        <v>28132</v>
       </c>
     </row>
     <row r="170">
@@ -9201,7 +9261,7 @@
         <v>4721</v>
       </c>
       <c r="C170" t="n">
-        <v>4337</v>
+        <v>4339</v>
       </c>
       <c r="D170" t="n">
         <v>5247</v>
@@ -9222,7 +9282,7 @@
         <v>48</v>
       </c>
       <c r="J170" t="n">
-        <v>19259</v>
+        <v>19261</v>
       </c>
     </row>
     <row r="171">
@@ -9262,10 +9322,10 @@
         <v>45717</v>
       </c>
       <c r="B172" t="n">
-        <v>6928</v>
+        <v>6933</v>
       </c>
       <c r="C172" t="n">
-        <v>5560</v>
+        <v>5561</v>
       </c>
       <c r="D172" t="n">
         <v>5308</v>
@@ -9286,7 +9346,7 @@
         <v>79</v>
       </c>
       <c r="J172" t="n">
-        <v>23857</v>
+        <v>23863</v>
       </c>
     </row>
     <row r="173">
@@ -9294,7 +9354,7 @@
         <v>45748</v>
       </c>
       <c r="B173" t="n">
-        <v>5650</v>
+        <v>5652</v>
       </c>
       <c r="C173" t="n">
         <v>4697</v>
@@ -9309,7 +9369,7 @@
         <v>2434</v>
       </c>
       <c r="G173" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H173" t="n">
         <v>310</v>
@@ -9318,7 +9378,7 @@
         <v>83</v>
       </c>
       <c r="J173" t="n">
-        <v>21019</v>
+        <v>21022</v>
       </c>
     </row>
     <row r="174">
@@ -9326,16 +9386,16 @@
         <v>45778</v>
       </c>
       <c r="B174" t="n">
-        <v>5672</v>
+        <v>5676</v>
       </c>
       <c r="C174" t="n">
-        <v>4851</v>
+        <v>4860</v>
       </c>
       <c r="D174" t="n">
-        <v>5924</v>
+        <v>5930</v>
       </c>
       <c r="E174" t="n">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="F174" t="n">
         <v>2610</v>
@@ -9350,7 +9410,7 @@
         <v>93</v>
       </c>
       <c r="J174" t="n">
-        <v>21559</v>
+        <v>21579</v>
       </c>
     </row>
     <row r="175">
@@ -9358,7 +9418,7 @@
         <v>45809</v>
       </c>
       <c r="B175" t="n">
-        <v>4879</v>
+        <v>4880</v>
       </c>
       <c r="C175" t="n">
         <v>3818</v>
@@ -9382,7 +9442,7 @@
         <v>54</v>
       </c>
       <c r="J175" t="n">
-        <v>17654</v>
+        <v>17655</v>
       </c>
     </row>
     <row r="176">
@@ -9390,19 +9450,19 @@
         <v>45839</v>
       </c>
       <c r="B176" t="n">
-        <v>5838</v>
+        <v>5840</v>
       </c>
       <c r="C176" t="n">
-        <v>5046</v>
+        <v>5049</v>
       </c>
       <c r="D176" t="n">
-        <v>5834</v>
+        <v>5835</v>
       </c>
       <c r="E176" t="n">
         <v>2190</v>
       </c>
       <c r="F176" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="G176" t="n">
         <v>440</v>
@@ -9414,7 +9474,7 @@
         <v>140</v>
       </c>
       <c r="J176" t="n">
-        <v>21875</v>
+        <v>21882</v>
       </c>
     </row>
     <row r="177">
@@ -9422,19 +9482,19 @@
         <v>45870</v>
       </c>
       <c r="B177" t="n">
-        <v>5378</v>
+        <v>5381</v>
       </c>
       <c r="C177" t="n">
-        <v>4803</v>
+        <v>4831</v>
       </c>
       <c r="D177" t="n">
-        <v>5110</v>
+        <v>5113</v>
       </c>
       <c r="E177" t="n">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="F177" t="n">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="G177" t="n">
         <v>397</v>
@@ -9443,10 +9503,10 @@
         <v>385</v>
       </c>
       <c r="I177" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J177" t="n">
-        <v>19869</v>
+        <v>19908</v>
       </c>
     </row>
     <row r="178">
@@ -9454,19 +9514,19 @@
         <v>45901</v>
       </c>
       <c r="B178" t="n">
-        <v>6466</v>
+        <v>6480</v>
       </c>
       <c r="C178" t="n">
-        <v>5205</v>
+        <v>5234</v>
       </c>
       <c r="D178" t="n">
-        <v>5845</v>
+        <v>5873</v>
       </c>
       <c r="E178" t="n">
-        <v>2199</v>
+        <v>2212</v>
       </c>
       <c r="F178" t="n">
-        <v>2197</v>
+        <v>2202</v>
       </c>
       <c r="G178" t="n">
         <v>495</v>
@@ -9478,7 +9538,7 @@
         <v>94</v>
       </c>
       <c r="J178" t="n">
-        <v>22904</v>
+        <v>22993</v>
       </c>
     </row>
     <row r="179">
@@ -9486,31 +9546,31 @@
         <v>45931</v>
       </c>
       <c r="B179" t="n">
-        <v>6982</v>
+        <v>6996</v>
       </c>
       <c r="C179" t="n">
-        <v>6101</v>
+        <v>6143</v>
       </c>
       <c r="D179" t="n">
-        <v>6100</v>
+        <v>6113</v>
       </c>
       <c r="E179" t="n">
-        <v>2256</v>
+        <v>2264</v>
       </c>
       <c r="F179" t="n">
-        <v>2689</v>
+        <v>2690</v>
       </c>
       <c r="G179" t="n">
         <v>478</v>
       </c>
       <c r="H179" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="I179" t="n">
         <v>99</v>
       </c>
       <c r="J179" t="n">
-        <v>25132</v>
+        <v>25212</v>
       </c>
     </row>
     <row r="180">
@@ -9518,31 +9578,31 @@
         <v>45962</v>
       </c>
       <c r="B180" t="n">
-        <v>7721</v>
+        <v>7737</v>
       </c>
       <c r="C180" t="n">
-        <v>5772</v>
+        <v>5795</v>
       </c>
       <c r="D180" t="n">
-        <v>6364</v>
+        <v>6388</v>
       </c>
       <c r="E180" t="n">
-        <v>2406</v>
+        <v>2412</v>
       </c>
       <c r="F180" t="n">
-        <v>2905</v>
+        <v>2909</v>
       </c>
       <c r="G180" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H180" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I180" t="n">
         <v>105</v>
       </c>
       <c r="J180" t="n">
-        <v>26152</v>
+        <v>26228</v>
       </c>
     </row>
     <row r="181">
@@ -9550,31 +9610,31 @@
         <v>45992</v>
       </c>
       <c r="B181" t="n">
-        <v>8740</v>
+        <v>8763</v>
       </c>
       <c r="C181" t="n">
-        <v>6703</v>
+        <v>6734</v>
       </c>
       <c r="D181" t="n">
-        <v>6741</v>
+        <v>6762</v>
       </c>
       <c r="E181" t="n">
-        <v>2734</v>
+        <v>2746</v>
       </c>
       <c r="F181" t="n">
-        <v>2909</v>
+        <v>2914</v>
       </c>
       <c r="G181" t="n">
         <v>513</v>
       </c>
       <c r="H181" t="n">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="I181" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J181" t="n">
-        <v>29075</v>
+        <v>29171</v>
       </c>
     </row>
     <row r="182">
@@ -9582,22 +9642,22 @@
         <v>46023</v>
       </c>
       <c r="B182" t="n">
-        <v>5182</v>
+        <v>5192</v>
       </c>
       <c r="C182" t="n">
-        <v>4037</v>
+        <v>4086</v>
       </c>
       <c r="D182" t="n">
-        <v>4875</v>
+        <v>4891</v>
       </c>
       <c r="E182" t="n">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="F182" t="n">
-        <v>2365</v>
+        <v>2369</v>
       </c>
       <c r="G182" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H182" t="n">
         <v>292</v>
@@ -9606,7 +9666,7 @@
         <v>54</v>
       </c>
       <c r="J182" t="n">
-        <v>18716</v>
+        <v>18801</v>
       </c>
     </row>
     <row r="183">
@@ -9614,31 +9674,31 @@
         <v>46054</v>
       </c>
       <c r="B183" t="n">
-        <v>7484</v>
+        <v>7498</v>
       </c>
       <c r="C183" t="n">
-        <v>6041</v>
+        <v>6100</v>
       </c>
       <c r="D183" t="n">
-        <v>6727</v>
+        <v>6747</v>
       </c>
       <c r="E183" t="n">
-        <v>2526</v>
+        <v>2538</v>
       </c>
       <c r="F183" t="n">
-        <v>3036</v>
+        <v>3056</v>
       </c>
       <c r="G183" t="n">
         <v>432</v>
       </c>
       <c r="H183" t="n">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="I183" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J183" t="n">
-        <v>26757</v>
+        <v>26891</v>
       </c>
     </row>
     <row r="184">
@@ -9646,31 +9706,31 @@
         <v>46082</v>
       </c>
       <c r="B184" t="n">
-        <v>9797</v>
+        <v>9829</v>
       </c>
       <c r="C184" t="n">
-        <v>6722</v>
+        <v>6813</v>
       </c>
       <c r="D184" t="n">
-        <v>8716</v>
+        <v>8756</v>
       </c>
       <c r="E184" t="n">
-        <v>3103</v>
+        <v>3116</v>
       </c>
       <c r="F184" t="n">
-        <v>3457</v>
+        <v>3479</v>
       </c>
       <c r="G184" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H184" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="I184" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J184" t="n">
-        <v>32876</v>
+        <v>33079</v>
       </c>
     </row>
     <row r="185">
@@ -9678,31 +9738,31 @@
         <v>46113</v>
       </c>
       <c r="B185" t="n">
-        <v>12796</v>
+        <v>12929</v>
       </c>
       <c r="C185" t="n">
-        <v>8903</v>
+        <v>9136</v>
       </c>
       <c r="D185" t="n">
-        <v>10328</v>
+        <v>10406</v>
       </c>
       <c r="E185" t="n">
-        <v>3927</v>
+        <v>3961</v>
       </c>
       <c r="F185" t="n">
-        <v>4152</v>
+        <v>4201</v>
       </c>
       <c r="G185" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="H185" t="n">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="I185" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J185" t="n">
-        <v>41685</v>
+        <v>42226</v>
       </c>
     </row>
     <row r="186">
@@ -9710,31 +9770,31 @@
         <v>46143</v>
       </c>
       <c r="B186" t="n">
-        <v>6537</v>
+        <v>6634</v>
       </c>
       <c r="C186" t="n">
-        <v>5292</v>
+        <v>5508</v>
       </c>
       <c r="D186" t="n">
-        <v>7013</v>
+        <v>7085</v>
       </c>
       <c r="E186" t="n">
-        <v>2464</v>
+        <v>2492</v>
       </c>
       <c r="F186" t="n">
-        <v>3666</v>
+        <v>3734</v>
       </c>
       <c r="G186" t="n">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="H186" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="I186" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J186" t="n">
-        <v>25862</v>
+        <v>26361</v>
       </c>
     </row>
     <row r="187">
@@ -9742,31 +9802,31 @@
         <v>46174</v>
       </c>
       <c r="B187" t="n">
-        <v>8105</v>
+        <v>8386</v>
       </c>
       <c r="C187" t="n">
-        <v>4921</v>
+        <v>5360</v>
       </c>
       <c r="D187" t="n">
-        <v>8800</v>
+        <v>8948</v>
       </c>
       <c r="E187" t="n">
-        <v>2361</v>
+        <v>2442</v>
       </c>
       <c r="F187" t="n">
-        <v>3586</v>
+        <v>3673</v>
       </c>
       <c r="G187" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H187" t="n">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="I187" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J187" t="n">
-        <v>28711</v>
+        <v>29763</v>
       </c>
     </row>
     <row r="188">
@@ -9774,31 +9834,31 @@
         <v>46204</v>
       </c>
       <c r="B188" t="n">
-        <v>7310</v>
+        <v>7859</v>
       </c>
       <c r="C188" t="n">
-        <v>4815</v>
+        <v>5654</v>
       </c>
       <c r="D188" t="n">
-        <v>8345</v>
+        <v>8670</v>
       </c>
       <c r="E188" t="n">
-        <v>2207</v>
+        <v>2367</v>
       </c>
       <c r="F188" t="n">
-        <v>3991</v>
+        <v>4182</v>
       </c>
       <c r="G188" t="n">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="H188" t="n">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="I188" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="J188" t="n">
-        <v>27651</v>
+        <v>29785</v>
       </c>
     </row>
     <row r="189">
@@ -9806,31 +9866,63 @@
         <v>46235</v>
       </c>
       <c r="B189" t="n">
-        <v>4327</v>
+        <v>6707</v>
       </c>
       <c r="C189" t="n">
-        <v>1576</v>
+        <v>4111</v>
       </c>
       <c r="D189" t="n">
-        <v>4904</v>
+        <v>6851</v>
       </c>
       <c r="E189" t="n">
-        <v>1408</v>
+        <v>2174</v>
       </c>
       <c r="F189" t="n">
-        <v>2554</v>
+        <v>3689</v>
       </c>
       <c r="G189" t="n">
-        <v>332</v>
+        <v>470</v>
       </c>
       <c r="H189" t="n">
-        <v>239</v>
+        <v>384</v>
       </c>
       <c r="I189" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="J189" t="n">
-        <v>15376</v>
+        <v>24467</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B190" t="n">
+        <v>4753</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1487</v>
+      </c>
+      <c r="D190" t="n">
+        <v>4951</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1461</v>
+      </c>
+      <c r="F190" t="n">
+        <v>2621</v>
+      </c>
+      <c r="G190" t="n">
+        <v>275</v>
+      </c>
+      <c r="H190" t="n">
+        <v>280</v>
+      </c>
+      <c r="I190" t="n">
+        <v>32</v>
+      </c>
+      <c r="J190" t="n">
+        <v>15860</v>
       </c>
     </row>
   </sheetData>
@@ -9844,7 +9936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J189"/>
+  <dimension ref="A1:J190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15240,7 +15332,7 @@
         <v>1.23</v>
       </c>
       <c r="J168" t="n">
-        <v>273.69</v>
+        <v>273.7</v>
       </c>
     </row>
     <row r="169">
@@ -15248,7 +15340,7 @@
         <v>45627</v>
       </c>
       <c r="B169" t="n">
-        <v>106.24</v>
+        <v>106.26</v>
       </c>
       <c r="C169" t="n">
         <v>69.52</v>
@@ -15272,7 +15364,7 @@
         <v>2.02</v>
       </c>
       <c r="J169" t="n">
-        <v>322.64</v>
+        <v>322.66</v>
       </c>
     </row>
     <row r="170">
@@ -15283,7 +15375,7 @@
         <v>46.55</v>
       </c>
       <c r="C170" t="n">
-        <v>37.24</v>
+        <v>37.25</v>
       </c>
       <c r="D170" t="n">
         <v>53.08</v>
@@ -15304,7 +15396,7 @@
         <v>0.78</v>
       </c>
       <c r="J170" t="n">
-        <v>180.36</v>
+        <v>180.37</v>
       </c>
     </row>
     <row r="171">
@@ -15344,10 +15436,10 @@
         <v>45717</v>
       </c>
       <c r="B172" t="n">
-        <v>74.09</v>
+        <v>74.28</v>
       </c>
       <c r="C172" t="n">
-        <v>52.9</v>
+        <v>52.93</v>
       </c>
       <c r="D172" t="n">
         <v>57.01</v>
@@ -15368,7 +15460,7 @@
         <v>1.48</v>
       </c>
       <c r="J172" t="n">
-        <v>243.24</v>
+        <v>243.46</v>
       </c>
     </row>
     <row r="173">
@@ -15376,7 +15468,7 @@
         <v>45748</v>
       </c>
       <c r="B173" t="n">
-        <v>57.37</v>
+        <v>57.38</v>
       </c>
       <c r="C173" t="n">
         <v>42.54</v>
@@ -15391,7 +15483,7 @@
         <v>19.4</v>
       </c>
       <c r="G173" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="H173" t="n">
         <v>3.31</v>
@@ -15400,7 +15492,7 @@
         <v>1.18</v>
       </c>
       <c r="J173" t="n">
-        <v>206.71</v>
+        <v>206.73</v>
       </c>
     </row>
     <row r="174">
@@ -15408,16 +15500,16 @@
         <v>45778</v>
       </c>
       <c r="B174" t="n">
-        <v>57.5</v>
+        <v>57.54</v>
       </c>
       <c r="C174" t="n">
-        <v>44.39</v>
+        <v>44.46</v>
       </c>
       <c r="D174" t="n">
-        <v>61.52</v>
+        <v>61.71</v>
       </c>
       <c r="E174" t="n">
-        <v>18.99</v>
+        <v>19.02</v>
       </c>
       <c r="F174" t="n">
         <v>21.48</v>
@@ -15432,7 +15524,7 @@
         <v>1.43</v>
       </c>
       <c r="J174" t="n">
-        <v>212.68</v>
+        <v>213.01</v>
       </c>
     </row>
     <row r="175">
@@ -15440,7 +15532,7 @@
         <v>45809</v>
       </c>
       <c r="B175" t="n">
-        <v>49.72</v>
+        <v>49.78</v>
       </c>
       <c r="C175" t="n">
         <v>34.09</v>
@@ -15464,7 +15556,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="J175" t="n">
-        <v>172.91</v>
+        <v>172.97</v>
       </c>
     </row>
     <row r="176">
@@ -15472,13 +15564,13 @@
         <v>45839</v>
       </c>
       <c r="B176" t="n">
-        <v>62.63</v>
+        <v>62.65</v>
       </c>
       <c r="C176" t="n">
-        <v>45.54</v>
+        <v>45.56</v>
       </c>
       <c r="D176" t="n">
-        <v>61.29</v>
+        <v>61.3</v>
       </c>
       <c r="E176" t="n">
         <v>24.31</v>
@@ -15496,7 +15588,7 @@
         <v>2.08</v>
       </c>
       <c r="J176" t="n">
-        <v>222.74</v>
+        <v>222.8</v>
       </c>
     </row>
     <row r="177">
@@ -15504,19 +15596,19 @@
         <v>45870</v>
       </c>
       <c r="B177" t="n">
-        <v>57.18</v>
+        <v>57.21</v>
       </c>
       <c r="C177" t="n">
-        <v>43.56</v>
+        <v>43.68</v>
       </c>
       <c r="D177" t="n">
-        <v>53.62</v>
+        <v>53.72</v>
       </c>
       <c r="E177" t="n">
-        <v>19.44</v>
+        <v>19.46</v>
       </c>
       <c r="F177" t="n">
-        <v>18.05</v>
+        <v>18.17</v>
       </c>
       <c r="G177" t="n">
         <v>4.01</v>
@@ -15528,7 +15620,7 @@
         <v>1.44</v>
       </c>
       <c r="J177" t="n">
-        <v>201.55</v>
+        <v>201.94</v>
       </c>
     </row>
     <row r="178">
@@ -15536,19 +15628,19 @@
         <v>45901</v>
       </c>
       <c r="B178" t="n">
-        <v>70.06</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="C178" t="n">
-        <v>49.08</v>
+        <v>49.47</v>
       </c>
       <c r="D178" t="n">
-        <v>61.73</v>
+        <v>62</v>
       </c>
       <c r="E178" t="n">
-        <v>23.7</v>
+        <v>24.1</v>
       </c>
       <c r="F178" t="n">
-        <v>21.29</v>
+        <v>21.44</v>
       </c>
       <c r="G178" t="n">
         <v>5.04</v>
@@ -15560,7 +15652,7 @@
         <v>1.53</v>
       </c>
       <c r="J178" t="n">
-        <v>237.29</v>
+        <v>238.62</v>
       </c>
     </row>
     <row r="179">
@@ -15568,31 +15660,31 @@
         <v>45931</v>
       </c>
       <c r="B179" t="n">
-        <v>75.48999999999999</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="C179" t="n">
-        <v>58.06</v>
+        <v>58.23</v>
       </c>
       <c r="D179" t="n">
-        <v>66.44</v>
+        <v>66.59</v>
       </c>
       <c r="E179" t="n">
-        <v>25.08</v>
+        <v>25.19</v>
       </c>
       <c r="F179" t="n">
-        <v>25.58</v>
+        <v>25.6</v>
       </c>
       <c r="G179" t="n">
         <v>4.53</v>
       </c>
       <c r="H179" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I179" t="n">
         <v>1.39</v>
       </c>
       <c r="J179" t="n">
-        <v>262.08</v>
+        <v>262.84</v>
       </c>
     </row>
     <row r="180">
@@ -15600,31 +15692,31 @@
         <v>45962</v>
       </c>
       <c r="B180" t="n">
-        <v>85.23999999999999</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="C180" t="n">
-        <v>55.94</v>
+        <v>56.23</v>
       </c>
       <c r="D180" t="n">
-        <v>71.42</v>
+        <v>71.59</v>
       </c>
       <c r="E180" t="n">
-        <v>26.62</v>
+        <v>26.67</v>
       </c>
       <c r="F180" t="n">
-        <v>28.08</v>
+        <v>28.32</v>
       </c>
       <c r="G180" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="H180" t="n">
-        <v>5.3</v>
+        <v>5.31</v>
       </c>
       <c r="I180" t="n">
         <v>1.67</v>
       </c>
       <c r="J180" t="n">
-        <v>279.01</v>
+        <v>280.04</v>
       </c>
     </row>
     <row r="181">
@@ -15632,31 +15724,31 @@
         <v>45992</v>
       </c>
       <c r="B181" t="n">
-        <v>108.5</v>
+        <v>108.91</v>
       </c>
       <c r="C181" t="n">
-        <v>72</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D181" t="n">
-        <v>83.45</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="E181" t="n">
-        <v>35.39</v>
+        <v>35.68</v>
       </c>
       <c r="F181" t="n">
-        <v>31.49</v>
+        <v>31.66</v>
       </c>
       <c r="G181" t="n">
         <v>5.88</v>
       </c>
       <c r="H181" t="n">
-        <v>7.58</v>
+        <v>7.6</v>
       </c>
       <c r="I181" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="J181" t="n">
-        <v>346.56</v>
+        <v>348.28</v>
       </c>
     </row>
     <row r="182">
@@ -15664,22 +15756,22 @@
         <v>46023</v>
       </c>
       <c r="B182" t="n">
-        <v>53.82</v>
+        <v>53.92</v>
       </c>
       <c r="C182" t="n">
-        <v>33.98</v>
+        <v>34.26</v>
       </c>
       <c r="D182" t="n">
-        <v>49.27</v>
+        <v>49.48</v>
       </c>
       <c r="E182" t="n">
-        <v>16.53</v>
+        <v>16.56</v>
       </c>
       <c r="F182" t="n">
-        <v>21.65</v>
+        <v>21.7</v>
       </c>
       <c r="G182" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="H182" t="n">
         <v>3.3</v>
@@ -15688,7 +15780,7 @@
         <v>0.68</v>
       </c>
       <c r="J182" t="n">
-        <v>182.37</v>
+        <v>183.05</v>
       </c>
     </row>
     <row r="183">
@@ -15696,31 +15788,31 @@
         <v>46054</v>
       </c>
       <c r="B183" t="n">
-        <v>79.97</v>
+        <v>80.28</v>
       </c>
       <c r="C183" t="n">
-        <v>53.61</v>
+        <v>54.38</v>
       </c>
       <c r="D183" t="n">
-        <v>69.16</v>
+        <v>69.53</v>
       </c>
       <c r="E183" t="n">
-        <v>26.89</v>
+        <v>27.02</v>
       </c>
       <c r="F183" t="n">
-        <v>28.07</v>
+        <v>28.44</v>
       </c>
       <c r="G183" t="n">
         <v>4.6</v>
       </c>
       <c r="H183" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="I183" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="J183" t="n">
-        <v>268.34</v>
+        <v>270.44</v>
       </c>
     </row>
     <row r="184">
@@ -15728,31 +15820,31 @@
         <v>46082</v>
       </c>
       <c r="B184" t="n">
-        <v>108.43</v>
+        <v>108.96</v>
       </c>
       <c r="C184" t="n">
-        <v>63.25</v>
+        <v>64.08</v>
       </c>
       <c r="D184" t="n">
-        <v>94.22</v>
+        <v>94.83</v>
       </c>
       <c r="E184" t="n">
-        <v>35.24</v>
+        <v>35.38</v>
       </c>
       <c r="F184" t="n">
-        <v>33.35</v>
+        <v>33.56</v>
       </c>
       <c r="G184" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="H184" t="n">
-        <v>6</v>
+        <v>6.02</v>
       </c>
       <c r="I184" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="J184" t="n">
-        <v>346.83</v>
+        <v>349.19</v>
       </c>
     </row>
     <row r="185">
@@ -15760,31 +15852,31 @@
         <v>46113</v>
       </c>
       <c r="B185" t="n">
-        <v>153.08</v>
+        <v>155.2</v>
       </c>
       <c r="C185" t="n">
-        <v>93.44</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D185" t="n">
-        <v>124.15</v>
+        <v>125.2</v>
       </c>
       <c r="E185" t="n">
-        <v>47.75</v>
+        <v>48.31</v>
       </c>
       <c r="F185" t="n">
-        <v>44.21</v>
+        <v>44.75</v>
       </c>
       <c r="G185" t="n">
-        <v>7.09</v>
+        <v>7.11</v>
       </c>
       <c r="H185" t="n">
-        <v>10.03</v>
+        <v>10.17</v>
       </c>
       <c r="I185" t="n">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="J185" t="n">
-        <v>482.5</v>
+        <v>490.12</v>
       </c>
     </row>
     <row r="186">
@@ -15792,31 +15884,31 @@
         <v>46143</v>
       </c>
       <c r="B186" t="n">
-        <v>63.92</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C186" t="n">
-        <v>41.45</v>
+        <v>43.04</v>
       </c>
       <c r="D186" t="n">
-        <v>66.84</v>
+        <v>67.62</v>
       </c>
       <c r="E186" t="n">
-        <v>24.26</v>
+        <v>24.76</v>
       </c>
       <c r="F186" t="n">
-        <v>32.26</v>
+        <v>32.7</v>
       </c>
       <c r="G186" t="n">
-        <v>4.56</v>
+        <v>4.68</v>
       </c>
       <c r="H186" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="J186" t="n">
-        <v>238.13</v>
+        <v>242.63</v>
       </c>
     </row>
     <row r="187">
@@ -15824,31 +15916,31 @@
         <v>46174</v>
       </c>
       <c r="B187" t="n">
-        <v>83.44</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="C187" t="n">
-        <v>41.77</v>
+        <v>44.95</v>
       </c>
       <c r="D187" t="n">
-        <v>87.73999999999999</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E187" t="n">
-        <v>23.38</v>
+        <v>24.06</v>
       </c>
       <c r="F187" t="n">
-        <v>32.82</v>
+        <v>33.94</v>
       </c>
       <c r="G187" t="n">
-        <v>4.25</v>
+        <v>4.32</v>
       </c>
       <c r="H187" t="n">
-        <v>4.53</v>
+        <v>4.61</v>
       </c>
       <c r="I187" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="J187" t="n">
-        <v>279.34</v>
+        <v>289.66</v>
       </c>
     </row>
     <row r="188">
@@ -15856,31 +15948,31 @@
         <v>46204</v>
       </c>
       <c r="B188" t="n">
-        <v>74.56</v>
+        <v>80.56</v>
       </c>
       <c r="C188" t="n">
-        <v>40.15</v>
+        <v>46.92</v>
       </c>
       <c r="D188" t="n">
-        <v>82.29000000000001</v>
+        <v>85.58</v>
       </c>
       <c r="E188" t="n">
-        <v>22.28</v>
+        <v>24.22</v>
       </c>
       <c r="F188" t="n">
-        <v>35.72</v>
+        <v>38.11</v>
       </c>
       <c r="G188" t="n">
-        <v>4.14</v>
+        <v>4.47</v>
       </c>
       <c r="H188" t="n">
-        <v>5.38</v>
+        <v>5.74</v>
       </c>
       <c r="I188" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="J188" t="n">
-        <v>265.83</v>
+        <v>287.01</v>
       </c>
     </row>
     <row r="189">
@@ -15888,31 +15980,63 @@
         <v>46235</v>
       </c>
       <c r="B189" t="n">
-        <v>42.85</v>
+        <v>67.37</v>
       </c>
       <c r="C189" t="n">
-        <v>12.36</v>
+        <v>33.62</v>
       </c>
       <c r="D189" t="n">
-        <v>48.93</v>
+        <v>68.02</v>
       </c>
       <c r="E189" t="n">
-        <v>13.89</v>
+        <v>21.91</v>
       </c>
       <c r="F189" t="n">
-        <v>22.96</v>
+        <v>33.63</v>
       </c>
       <c r="G189" t="n">
-        <v>3.21</v>
+        <v>4.57</v>
       </c>
       <c r="H189" t="n">
-        <v>2.78</v>
+        <v>4.44</v>
       </c>
       <c r="I189" t="n">
-        <v>0.51</v>
+        <v>1.21</v>
       </c>
       <c r="J189" t="n">
-        <v>147.5</v>
+        <v>234.77</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B190" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="C190" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="D190" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="E190" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="F190" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="G190" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H190" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J190" t="n">
+        <v>153.23</v>
       </c>
     </row>
   </sheetData>
@@ -15926,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15986,19 +16110,19 @@
         <v>45839</v>
       </c>
       <c r="B2" t="n">
-        <v>10210</v>
+        <v>10220</v>
       </c>
       <c r="C2" t="n">
-        <v>5977</v>
+        <v>5978</v>
       </c>
       <c r="D2" t="n">
-        <v>5639</v>
+        <v>5640</v>
       </c>
       <c r="E2" t="n">
-        <v>4448</v>
+        <v>4449</v>
       </c>
       <c r="F2" t="n">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="G2" t="n">
         <v>376</v>
@@ -16010,7 +16134,7 @@
         <v>105</v>
       </c>
       <c r="J2" t="n">
-        <v>29509</v>
+        <v>29523</v>
       </c>
     </row>
     <row r="3">
@@ -16018,16 +16142,16 @@
         <v>45870</v>
       </c>
       <c r="B3" t="n">
-        <v>8456</v>
+        <v>8460</v>
       </c>
       <c r="C3" t="n">
-        <v>5266</v>
+        <v>5272</v>
       </c>
       <c r="D3" t="n">
-        <v>4531</v>
+        <v>4535</v>
       </c>
       <c r="E3" t="n">
-        <v>3285</v>
+        <v>3291</v>
       </c>
       <c r="F3" t="n">
         <v>3326</v>
@@ -16042,7 +16166,7 @@
         <v>92</v>
       </c>
       <c r="J3" t="n">
-        <v>25784</v>
+        <v>25804</v>
       </c>
     </row>
     <row r="4">
@@ -16050,31 +16174,31 @@
         <v>45901</v>
       </c>
       <c r="B4" t="n">
-        <v>10570</v>
+        <v>10600</v>
       </c>
       <c r="C4" t="n">
-        <v>6195</v>
+        <v>6221</v>
       </c>
       <c r="D4" t="n">
-        <v>5559</v>
+        <v>5570</v>
       </c>
       <c r="E4" t="n">
-        <v>3983</v>
+        <v>4002</v>
       </c>
       <c r="F4" t="n">
-        <v>3704</v>
+        <v>3711</v>
       </c>
       <c r="G4" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H4" t="n">
         <v>580</v>
       </c>
       <c r="I4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J4" t="n">
-        <v>31040</v>
+        <v>31137</v>
       </c>
     </row>
     <row r="5">
@@ -16082,22 +16206,22 @@
         <v>45931</v>
       </c>
       <c r="B5" t="n">
-        <v>12066</v>
+        <v>12092</v>
       </c>
       <c r="C5" t="n">
-        <v>7727</v>
+        <v>7770</v>
       </c>
       <c r="D5" t="n">
-        <v>6798</v>
+        <v>6814</v>
       </c>
       <c r="E5" t="n">
-        <v>4359</v>
+        <v>4375</v>
       </c>
       <c r="F5" t="n">
-        <v>4554</v>
+        <v>4558</v>
       </c>
       <c r="G5" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H5" t="n">
         <v>667</v>
@@ -16106,7 +16230,7 @@
         <v>82</v>
       </c>
       <c r="J5" t="n">
-        <v>36626</v>
+        <v>36732</v>
       </c>
     </row>
     <row r="6">
@@ -16114,31 +16238,31 @@
         <v>45962</v>
       </c>
       <c r="B6" t="n">
-        <v>13201</v>
+        <v>13238</v>
       </c>
       <c r="C6" t="n">
-        <v>7921</v>
+        <v>7961</v>
       </c>
       <c r="D6" t="n">
-        <v>7344</v>
+        <v>7359</v>
       </c>
       <c r="E6" t="n">
-        <v>4447</v>
+        <v>4467</v>
       </c>
       <c r="F6" t="n">
-        <v>4529</v>
+        <v>4537</v>
       </c>
       <c r="G6" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H6" t="n">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="I6" t="n">
         <v>114</v>
       </c>
       <c r="J6" t="n">
-        <v>38590</v>
+        <v>38714</v>
       </c>
     </row>
     <row r="7">
@@ -16146,31 +16270,31 @@
         <v>45992</v>
       </c>
       <c r="B7" t="n">
-        <v>15600</v>
+        <v>15652</v>
       </c>
       <c r="C7" t="n">
-        <v>10237</v>
+        <v>10292</v>
       </c>
       <c r="D7" t="n">
-        <v>8565</v>
+        <v>8586</v>
       </c>
       <c r="E7" t="n">
-        <v>4844</v>
+        <v>4867</v>
       </c>
       <c r="F7" t="n">
-        <v>4482</v>
+        <v>4494</v>
       </c>
       <c r="G7" t="n">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H7" t="n">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="I7" t="n">
         <v>155</v>
       </c>
       <c r="J7" t="n">
-        <v>45223</v>
+        <v>45398</v>
       </c>
     </row>
     <row r="8">
@@ -16178,22 +16302,22 @@
         <v>46023</v>
       </c>
       <c r="B8" t="n">
-        <v>9919</v>
+        <v>9942</v>
       </c>
       <c r="C8" t="n">
-        <v>5195</v>
+        <v>5248</v>
       </c>
       <c r="D8" t="n">
-        <v>5898</v>
+        <v>5907</v>
       </c>
       <c r="E8" t="n">
-        <v>3046</v>
+        <v>3057</v>
       </c>
       <c r="F8" t="n">
-        <v>3686</v>
+        <v>3691</v>
       </c>
       <c r="G8" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H8" t="n">
         <v>476</v>
@@ -16202,7 +16326,7 @@
         <v>51</v>
       </c>
       <c r="J8" t="n">
-        <v>28501</v>
+        <v>28606</v>
       </c>
     </row>
     <row r="9">
@@ -16210,31 +16334,31 @@
         <v>46054</v>
       </c>
       <c r="B9" t="n">
-        <v>14167</v>
+        <v>14209</v>
       </c>
       <c r="C9" t="n">
-        <v>8318</v>
+        <v>8388</v>
       </c>
       <c r="D9" t="n">
-        <v>8257</v>
+        <v>8267</v>
       </c>
       <c r="E9" t="n">
-        <v>4283</v>
+        <v>4294</v>
       </c>
       <c r="F9" t="n">
-        <v>4448</v>
+        <v>4458</v>
       </c>
       <c r="G9" t="n">
         <v>392</v>
       </c>
       <c r="H9" t="n">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="I9" t="n">
         <v>81</v>
       </c>
       <c r="J9" t="n">
-        <v>40664</v>
+        <v>40809</v>
       </c>
     </row>
     <row r="10">
@@ -16242,31 +16366,31 @@
         <v>46082</v>
       </c>
       <c r="B10" t="n">
-        <v>19894</v>
+        <v>19979</v>
       </c>
       <c r="C10" t="n">
-        <v>11530</v>
+        <v>11666</v>
       </c>
       <c r="D10" t="n">
-        <v>11343</v>
+        <v>11373</v>
       </c>
       <c r="E10" t="n">
-        <v>5468</v>
+        <v>5501</v>
       </c>
       <c r="F10" t="n">
-        <v>5233</v>
+        <v>5251</v>
       </c>
       <c r="G10" t="n">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="H10" t="n">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="I10" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J10" t="n">
-        <v>55032</v>
+        <v>55342</v>
       </c>
     </row>
     <row r="11">
@@ -16274,31 +16398,31 @@
         <v>46113</v>
       </c>
       <c r="B11" t="n">
-        <v>30753</v>
+        <v>31072</v>
       </c>
       <c r="C11" t="n">
-        <v>19253</v>
+        <v>19844</v>
       </c>
       <c r="D11" t="n">
-        <v>18030</v>
+        <v>18227</v>
       </c>
       <c r="E11" t="n">
-        <v>8361</v>
+        <v>8454</v>
       </c>
       <c r="F11" t="n">
-        <v>6701</v>
+        <v>6771</v>
       </c>
       <c r="G11" t="n">
-        <v>895</v>
+        <v>911</v>
       </c>
       <c r="H11" t="n">
-        <v>1576</v>
+        <v>1599</v>
       </c>
       <c r="I11" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="J11" t="n">
-        <v>85812</v>
+        <v>87128</v>
       </c>
     </row>
     <row r="12">
@@ -16306,31 +16430,31 @@
         <v>46143</v>
       </c>
       <c r="B12" t="n">
-        <v>7061</v>
+        <v>7164</v>
       </c>
       <c r="C12" t="n">
-        <v>4274</v>
+        <v>4454</v>
       </c>
       <c r="D12" t="n">
-        <v>4674</v>
+        <v>4727</v>
       </c>
       <c r="E12" t="n">
-        <v>2609</v>
+        <v>2643</v>
       </c>
       <c r="F12" t="n">
-        <v>3899</v>
+        <v>3940</v>
       </c>
       <c r="G12" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H12" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="I12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>23253</v>
+        <v>23679</v>
       </c>
     </row>
     <row r="13">
@@ -16338,31 +16462,31 @@
         <v>46174</v>
       </c>
       <c r="B13" t="n">
-        <v>9244</v>
+        <v>9718</v>
       </c>
       <c r="C13" t="n">
-        <v>4897</v>
+        <v>5412</v>
       </c>
       <c r="D13" t="n">
-        <v>6582</v>
+        <v>6728</v>
       </c>
       <c r="E13" t="n">
-        <v>2864</v>
+        <v>2997</v>
       </c>
       <c r="F13" t="n">
-        <v>3809</v>
+        <v>3941</v>
       </c>
       <c r="G13" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="H13" t="n">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="I13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J13" t="n">
-        <v>28354</v>
+        <v>29795</v>
       </c>
     </row>
     <row r="14">
@@ -16370,31 +16494,31 @@
         <v>46204</v>
       </c>
       <c r="B14" t="n">
-        <v>9352</v>
+        <v>10204</v>
       </c>
       <c r="C14" t="n">
-        <v>4747</v>
+        <v>5832</v>
       </c>
       <c r="D14" t="n">
-        <v>6608</v>
+        <v>7035</v>
       </c>
       <c r="E14" t="n">
-        <v>2999</v>
+        <v>3290</v>
       </c>
       <c r="F14" t="n">
-        <v>4059</v>
+        <v>4316</v>
       </c>
       <c r="G14" t="n">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="H14" t="n">
-        <v>628</v>
+        <v>691</v>
       </c>
       <c r="I14" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="J14" t="n">
-        <v>28751</v>
+        <v>31769</v>
       </c>
     </row>
     <row r="15">
@@ -16402,31 +16526,63 @@
         <v>46235</v>
       </c>
       <c r="B15" t="n">
-        <v>5019</v>
+        <v>9160</v>
       </c>
       <c r="C15" t="n">
-        <v>1105</v>
+        <v>4417</v>
       </c>
       <c r="D15" t="n">
-        <v>3498</v>
+        <v>6058</v>
       </c>
       <c r="E15" t="n">
-        <v>1601</v>
+        <v>3140</v>
       </c>
       <c r="F15" t="n">
-        <v>2111</v>
+        <v>3775</v>
       </c>
       <c r="G15" t="n">
-        <v>168</v>
+        <v>301</v>
       </c>
       <c r="H15" t="n">
-        <v>285</v>
+        <v>586</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J15" t="n">
-        <v>13810</v>
+        <v>27498</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5444</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1274</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3752</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1631</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2281</v>
+      </c>
+      <c r="G16" t="n">
+        <v>124</v>
+      </c>
+      <c r="H16" t="n">
+        <v>330</v>
+      </c>
+      <c r="I16" t="n">
+        <v>19</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14855</v>
       </c>
     </row>
   </sheetData>
